--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88787,15 +88775,17 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="B4771" t="inlineStr"/>
+      <c r="B4771" t="n">
+        <v>-3</v>
+      </c>
       <c r="C4771" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4771" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4771" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -88819,21 +88809,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2013-03-01 to 2026-03-22 | Publication days: 3653</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2013-03-01 to 2026-03-22 | Publication days: 3654</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88841,22 +88831,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4771"/>
+  <dimension ref="A1:E4772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88786,6 +88786,23 @@
       </c>
       <c r="E4771" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4772">
+      <c r="A4772" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B4772" t="inlineStr"/>
+      <c r="C4772" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D4772" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E4772" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88818,7 +88835,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-22 | Publication days: 3654</t>
+          <t>Coverage: 2013-03-01 to 2026-03-23 | Publication days: 3654</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4772"/>
+  <dimension ref="A1:E4773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88802,6 +88802,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E4772" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4773">
+      <c r="A4773" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B4773" t="inlineStr"/>
+      <c r="C4773" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D4773" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E4773" t="b">
         <v>0</v>
       </c>
     </row>
@@ -88835,7 +88852,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-23 | Publication days: 3654</t>
+          <t>Coverage: 2013-03-01 to 2026-03-24 | Publication days: 3654</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4773"/>
+  <dimension ref="A1:E4774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88819,6 +88819,23 @@
         <v>-0.8</v>
       </c>
       <c r="E4773" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4774">
+      <c r="A4774" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B4774" t="inlineStr"/>
+      <c r="C4774" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D4774" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E4774" t="b">
         <v>0</v>
       </c>
     </row>
@@ -88852,7 +88869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-24 | Publication days: 3654</t>
+          <t>Coverage: 2013-03-01 to 2026-03-25 | Publication days: 3654</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -88408,13 +88408,13 @@
         </is>
       </c>
       <c r="B4751" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C4751" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4751" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4751" t="b">
         <v>1</v>
@@ -88430,10 +88430,10 @@
         <v>0</v>
       </c>
       <c r="C4752" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4752" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E4752" t="b">
         <v>1</v>
@@ -88449,10 +88449,10 @@
         <v>0</v>
       </c>
       <c r="C4753" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4753" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E4753" t="b">
         <v>1</v>
@@ -88465,13 +88465,13 @@
         </is>
       </c>
       <c r="B4754" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C4754" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D4754" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E4754" t="b">
         <v>1</v>
@@ -88487,10 +88487,10 @@
         <v>0</v>
       </c>
       <c r="C4755" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D4755" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E4755" t="b">
         <v>1</v>
@@ -88504,10 +88504,10 @@
       </c>
       <c r="B4756" t="inlineStr"/>
       <c r="C4756" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D4756" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E4756" t="b">
         <v>0</v>
@@ -88521,10 +88521,10 @@
       </c>
       <c r="B4757" t="inlineStr"/>
       <c r="C4757" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4757" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E4757" t="b">
         <v>0</v>
@@ -88540,10 +88540,10 @@
         <v>-3</v>
       </c>
       <c r="C4758" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4758" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E4758" t="b">
         <v>1</v>
@@ -88559,10 +88559,10 @@
         <v>0</v>
       </c>
       <c r="C4759" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4759" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E4759" t="b">
         <v>1</v>
@@ -88578,10 +88578,10 @@
         <v>0</v>
       </c>
       <c r="C4760" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4760" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E4760" t="b">
         <v>1</v>
@@ -88600,7 +88600,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4761" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E4761" t="b">
         <v>1</v>
@@ -88619,7 +88619,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4762" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E4762" t="b">
         <v>1</v>
@@ -88636,7 +88636,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4763" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E4763" t="b">
         <v>0</v>
@@ -88653,7 +88653,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4764" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E4764" t="b">
         <v>0</v>
@@ -88672,7 +88672,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4765" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4765" t="b">
         <v>1</v>
@@ -88691,7 +88691,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4766" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4766" t="b">
         <v>1</v>
@@ -88710,7 +88710,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4767" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4767" t="b">
         <v>1</v>
@@ -88723,13 +88723,13 @@
         </is>
       </c>
       <c r="B4768" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C4768" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4768" t="n">
-        <v>-0.5</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4768" t="b">
         <v>1</v>
@@ -88741,15 +88741,17 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="B4769" t="inlineStr"/>
+      <c r="B4769" t="n">
+        <v>0</v>
+      </c>
       <c r="C4769" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4769" t="n">
-        <v>-0.5</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4769" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4770">
@@ -88760,10 +88762,10 @@
       </c>
       <c r="B4770" t="inlineStr"/>
       <c r="C4770" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4770" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E4770" t="b">
         <v>0</v>
@@ -88779,10 +88781,10 @@
         <v>-3</v>
       </c>
       <c r="C4771" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D4771" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E4771" t="b">
         <v>1</v>
@@ -88794,15 +88796,17 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="B4772" t="inlineStr"/>
+      <c r="B4772" t="n">
+        <v>0</v>
+      </c>
       <c r="C4772" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4772" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E4772" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4773">
@@ -88811,15 +88815,17 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B4773" t="inlineStr"/>
+      <c r="B4773" t="n">
+        <v>0</v>
+      </c>
       <c r="C4773" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4773" t="n">
-        <v>-0.8</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4773" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4774">
@@ -88828,15 +88834,17 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="B4774" t="inlineStr"/>
+      <c r="B4774" t="n">
+        <v>0</v>
+      </c>
       <c r="C4774" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4774" t="n">
-        <v>-0.9</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4774" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -88869,7 +88877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-25 | Publication days: 3654</t>
+          <t>Coverage: 2013-03-01 to 2026-03-25 | Publication days: 3658</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88868,21 +88880,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2013-03-01 to 2026-03-25 | Publication days: 3658</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88890,22 +88902,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4774"/>
+  <dimension ref="A1:E4775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88857,6 +88845,23 @@
       </c>
       <c r="E4774" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4775">
+      <c r="A4775" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B4775" t="inlineStr"/>
+      <c r="C4775" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D4775" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E4775" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88880,21 +88885,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2013-03-01 to 2026-03-25 | Publication days: 3658</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2013-03-01 to 2026-03-26 | Publication days: 3658</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88902,22 +88907,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88885,21 +88897,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2013-03-01 to 2026-03-26 | Publication days: 3658</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88907,22 +88919,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88865,7 +88853,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B4775" t="inlineStr"/>
+      <c r="B4775" t="n">
+        <v>0</v>
+      </c>
       <c r="C4775" t="n">
         <v>-0.4285714285714285</v>
       </c>
@@ -88873,7 +88863,7 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E4775" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -88897,21 +88887,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2013-03-01 to 2026-03-26 | Publication days: 3658</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2013-03-01 to 2026-03-26 | Publication days: 3659</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88919,22 +88909,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88887,21 +88899,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2013-03-01 to 2026-03-26 | Publication days: 3659</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88909,22 +88921,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4775"/>
+  <dimension ref="A1:E4776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -88876,6 +88864,23 @@
       </c>
       <c r="E4775" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4776">
+      <c r="A4776" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B4776" t="inlineStr"/>
+      <c r="C4776" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D4776" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E4776" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88899,21 +88904,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Japan WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2013-03-01 to 2026-03-26 | Publication days: 3659</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2013-03-01 to 2026-03-27 | Publication days: 3659</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -88921,22 +88926,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -88872,15 +88872,17 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B4776" t="inlineStr"/>
+      <c r="B4776" t="n">
+        <v>-2</v>
+      </c>
       <c r="C4776" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4776" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4776" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -88913,7 +88915,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-27 | Publication days: 3659</t>
+          <t>Coverage: 2013-03-01 to 2026-03-27 | Publication days: 3660</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4776"/>
+  <dimension ref="A1:E4777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88883,6 +88883,23 @@
       </c>
       <c r="E4776" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4777">
+      <c r="A4777" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B4777" t="inlineStr"/>
+      <c r="C4777" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D4777" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E4777" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88915,7 +88932,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-27 | Publication days: 3660</t>
+          <t>Coverage: 2013-03-01 to 2026-03-28 | Publication days: 3660</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4777"/>
+  <dimension ref="A1:E4778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88891,14 +88891,33 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="B4777" t="inlineStr"/>
+      <c r="B4777" t="n">
+        <v>0</v>
+      </c>
       <c r="C4777" t="n">
-        <v>-1</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4777" t="n">
-        <v>-0.8</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4777" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4778">
+      <c r="A4778" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B4778" t="inlineStr"/>
+      <c r="C4778" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D4778" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E4778" t="b">
         <v>0</v>
       </c>
     </row>
@@ -88932,7 +88951,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-28 | Publication days: 3660</t>
+          <t>Coverage: 2013-03-01 to 2026-03-29 | Publication days: 3661</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4778"/>
+  <dimension ref="A1:E4779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88918,6 +88918,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E4778" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4779">
+      <c r="A4779" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4779" t="inlineStr"/>
+      <c r="C4779" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D4779" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E4779" t="b">
         <v>0</v>
       </c>
     </row>
@@ -88951,7 +88968,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-29 | Publication days: 3661</t>
+          <t>Coverage: 2013-03-01 to 2026-03-30 | Publication days: 3661</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4779"/>
+  <dimension ref="A1:E4780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88935,6 +88935,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E4779" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4780">
+      <c r="A4780" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B4780" t="inlineStr"/>
+      <c r="C4780" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D4780" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E4780" t="b">
         <v>0</v>
       </c>
     </row>
@@ -88968,7 +88985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-30 | Publication days: 3661</t>
+          <t>Coverage: 2013-03-01 to 2026-03-31 | Publication days: 3661</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4780"/>
+  <dimension ref="A1:E4781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88927,7 +88927,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="B4779" t="inlineStr"/>
+      <c r="B4779" t="n">
+        <v>0</v>
+      </c>
       <c r="C4779" t="n">
         <v>-0.2857142857142857</v>
       </c>
@@ -88935,7 +88937,7 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E4779" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4780">
@@ -88944,15 +88946,36 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="B4780" t="inlineStr"/>
+      <c r="B4780" t="n">
+        <v>-2</v>
+      </c>
       <c r="C4780" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4780" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E4780" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4781">
+      <c r="A4781" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B4781" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4781" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D4781" t="n">
         <v>-0.6666666666666666</v>
       </c>
-      <c r="E4780" t="b">
-        <v>0</v>
+      <c r="E4781" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -88985,7 +89008,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-03-31 | Publication days: 3661</t>
+          <t>Coverage: 2013-03-01 to 2026-04-01 | Publication days: 3664</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4781"/>
+  <dimension ref="A1:E4782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88446,13 +88446,13 @@
         </is>
       </c>
       <c r="B4753" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C4753" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4753" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4753" t="b">
         <v>1</v>
@@ -88465,13 +88465,13 @@
         </is>
       </c>
       <c r="B4754" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C4754" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4754" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4754" t="b">
         <v>1</v>
@@ -88487,10 +88487,10 @@
         <v>0</v>
       </c>
       <c r="C4755" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4755" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4755" t="b">
         <v>1</v>
@@ -88504,10 +88504,10 @@
       </c>
       <c r="B4756" t="inlineStr"/>
       <c r="C4756" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4756" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4756" t="b">
         <v>0</v>
@@ -88521,10 +88521,10 @@
       </c>
       <c r="B4757" t="inlineStr"/>
       <c r="C4757" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4757" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4757" t="b">
         <v>0</v>
@@ -88540,10 +88540,10 @@
         <v>-3</v>
       </c>
       <c r="C4758" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D4758" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4758" t="b">
         <v>1</v>
@@ -88559,10 +88559,10 @@
         <v>0</v>
       </c>
       <c r="C4759" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D4759" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4759" t="b">
         <v>1</v>
@@ -88578,10 +88578,10 @@
         <v>0</v>
       </c>
       <c r="C4760" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4760" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4760" t="b">
         <v>1</v>
@@ -88600,7 +88600,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4761" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4761" t="b">
         <v>1</v>
@@ -88619,7 +88619,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4762" t="n">
-        <v>-0.5</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4762" t="b">
         <v>1</v>
@@ -88636,7 +88636,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4763" t="n">
-        <v>-0.5</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4763" t="b">
         <v>0</v>
@@ -88653,7 +88653,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4764" t="n">
-        <v>-0.5</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4764" t="b">
         <v>0</v>
@@ -88672,7 +88672,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4765" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E4765" t="b">
         <v>1</v>
@@ -88691,7 +88691,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4766" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7</v>
       </c>
       <c r="E4766" t="b">
         <v>1</v>
@@ -88710,7 +88710,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4767" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7</v>
       </c>
       <c r="E4767" t="b">
         <v>1</v>
@@ -88729,7 +88729,7 @@
         <v>-1</v>
       </c>
       <c r="D4768" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7</v>
       </c>
       <c r="E4768" t="b">
         <v>1</v>
@@ -88748,7 +88748,7 @@
         <v>-1</v>
       </c>
       <c r="D4769" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7</v>
       </c>
       <c r="E4769" t="b">
         <v>1</v>
@@ -88765,7 +88765,7 @@
         <v>-1</v>
       </c>
       <c r="D4770" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4770" t="b">
         <v>0</v>
@@ -88784,7 +88784,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D4771" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4771" t="b">
         <v>1</v>
@@ -88803,7 +88803,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D4772" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4772" t="b">
         <v>1</v>
@@ -88822,7 +88822,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4773" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4773" t="b">
         <v>1</v>
@@ -88841,7 +88841,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4774" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4774" t="b">
         <v>1</v>
@@ -88860,7 +88860,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4775" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7</v>
       </c>
       <c r="E4775" t="b">
         <v>1</v>
@@ -88879,7 +88879,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4776" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4776" t="b">
         <v>1</v>
@@ -88898,7 +88898,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4777" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4777" t="b">
         <v>1</v>
@@ -88915,7 +88915,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4778" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4778" t="b">
         <v>0</v>
@@ -88934,7 +88934,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4779" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4779" t="b">
         <v>1</v>
@@ -88953,7 +88953,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D4780" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4780" t="b">
         <v>1</v>
@@ -88966,15 +88966,34 @@
         </is>
       </c>
       <c r="B4781" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C4781" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4781" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4781" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4782">
+      <c r="A4782" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B4782" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4782" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D4782" t="n">
+        <v>-0.7666666666666667</v>
+      </c>
+      <c r="E4782" t="b">
         <v>1</v>
       </c>
     </row>
@@ -89008,7 +89027,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-01 | Publication days: 3664</t>
+          <t>Coverage: 2013-03-01 to 2026-04-02 | Publication days: 3665</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4782"/>
+  <dimension ref="A1:E4783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88465,13 +88465,13 @@
         </is>
       </c>
       <c r="B4754" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C4754" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D4754" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4754" t="b">
         <v>1</v>
@@ -88487,10 +88487,10 @@
         <v>0</v>
       </c>
       <c r="C4755" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D4755" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4755" t="b">
         <v>1</v>
@@ -88504,10 +88504,10 @@
       </c>
       <c r="B4756" t="inlineStr"/>
       <c r="C4756" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D4756" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4756" t="b">
         <v>0</v>
@@ -88521,10 +88521,10 @@
       </c>
       <c r="B4757" t="inlineStr"/>
       <c r="C4757" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D4757" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4757" t="b">
         <v>0</v>
@@ -88540,10 +88540,10 @@
         <v>-3</v>
       </c>
       <c r="C4758" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4758" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4758" t="b">
         <v>1</v>
@@ -88559,10 +88559,10 @@
         <v>0</v>
       </c>
       <c r="C4759" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4759" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4759" t="b">
         <v>1</v>
@@ -88578,10 +88578,10 @@
         <v>0</v>
       </c>
       <c r="C4760" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4760" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4760" t="b">
         <v>1</v>
@@ -88600,7 +88600,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4761" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4761" t="b">
         <v>1</v>
@@ -88619,7 +88619,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4762" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4762" t="b">
         <v>1</v>
@@ -88636,7 +88636,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4763" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4763" t="b">
         <v>0</v>
@@ -88653,7 +88653,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4764" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4764" t="b">
         <v>0</v>
@@ -88672,7 +88672,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4765" t="n">
-        <v>-0.6</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4765" t="b">
         <v>1</v>
@@ -88691,7 +88691,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4766" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4766" t="b">
         <v>1</v>
@@ -88710,7 +88710,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4767" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4767" t="b">
         <v>1</v>
@@ -88729,7 +88729,7 @@
         <v>-1</v>
       </c>
       <c r="D4768" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4768" t="b">
         <v>1</v>
@@ -88748,7 +88748,7 @@
         <v>-1</v>
       </c>
       <c r="D4769" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4769" t="b">
         <v>1</v>
@@ -88765,7 +88765,7 @@
         <v>-1</v>
       </c>
       <c r="D4770" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4770" t="b">
         <v>0</v>
@@ -88784,7 +88784,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D4771" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4771" t="b">
         <v>1</v>
@@ -88803,7 +88803,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D4772" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4772" t="b">
         <v>1</v>
@@ -88822,7 +88822,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4773" t="n">
-        <v>-0.8</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E4773" t="b">
         <v>1</v>
@@ -88841,7 +88841,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4774" t="n">
-        <v>-0.8</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E4774" t="b">
         <v>1</v>
@@ -88860,7 +88860,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4775" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4775" t="b">
         <v>1</v>
@@ -88879,7 +88879,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4776" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4776" t="b">
         <v>1</v>
@@ -88898,7 +88898,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4777" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4777" t="b">
         <v>1</v>
@@ -88915,7 +88915,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4778" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4778" t="b">
         <v>0</v>
@@ -88934,7 +88934,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4779" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4779" t="b">
         <v>1</v>
@@ -88953,7 +88953,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D4780" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4780" t="b">
         <v>1</v>
@@ -88972,7 +88972,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D4781" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4781" t="b">
         <v>1</v>
@@ -88991,9 +88991,28 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D4782" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E4782" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4783">
+      <c r="A4783" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B4783" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4783" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D4783" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E4783" t="b">
         <v>1</v>
       </c>
     </row>
@@ -89027,7 +89046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-02 | Publication days: 3665</t>
+          <t>Coverage: 2013-03-01 to 2026-04-03 | Publication days: 3666</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4783"/>
+  <dimension ref="A1:E4784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89014,6 +89014,23 @@
       </c>
       <c r="E4783" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4784">
+      <c r="A4784" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B4784" t="inlineStr"/>
+      <c r="C4784" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D4784" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E4784" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -89046,7 +89063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-03 | Publication days: 3666</t>
+          <t>Coverage: 2013-03-01 to 2026-04-04 | Publication days: 3666</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4784"/>
+  <dimension ref="A1:E4785"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89030,6 +89030,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E4784" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4785">
+      <c r="A4785" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B4785" t="inlineStr"/>
+      <c r="C4785" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D4785" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E4785" t="b">
         <v>0</v>
       </c>
     </row>
@@ -89063,7 +89080,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-04 | Publication days: 3666</t>
+          <t>Coverage: 2013-03-01 to 2026-04-05 | Publication days: 3666</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4785"/>
+  <dimension ref="A1:E4786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89047,6 +89047,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E4785" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4786">
+      <c r="A4786" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B4786" t="inlineStr"/>
+      <c r="C4786" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D4786" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E4786" t="b">
         <v>0</v>
       </c>
     </row>
@@ -89080,7 +89097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-05 | Publication days: 3666</t>
+          <t>Coverage: 2013-03-01 to 2026-04-06 | Publication days: 3666</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4786"/>
+  <dimension ref="A1:E4787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89064,6 +89064,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E4786" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4787">
+      <c r="A4787" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B4787" t="inlineStr"/>
+      <c r="C4787" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D4787" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E4787" t="b">
         <v>0</v>
       </c>
     </row>
@@ -89097,7 +89114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-06 | Publication days: 3666</t>
+          <t>Coverage: 2013-03-01 to 2026-04-07 | Publication days: 3666</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4787"/>
+  <dimension ref="A1:E4788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89081,6 +89081,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E4787" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4788">
+      <c r="A4788" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B4788" t="inlineStr"/>
+      <c r="C4788" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4788" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E4788" t="b">
         <v>0</v>
       </c>
     </row>
@@ -89114,7 +89131,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-07 | Publication days: 3666</t>
+          <t>Coverage: 2013-03-01 to 2026-04-08 | Publication days: 3666</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4788"/>
+  <dimension ref="A1:E4789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88408,13 +88408,13 @@
         </is>
       </c>
       <c r="B4751" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C4751" t="n">
-        <v>-1</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4751" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E4751" t="b">
         <v>1</v>
@@ -88430,10 +88430,10 @@
         <v>0</v>
       </c>
       <c r="C4752" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D4752" t="n">
-        <v>-0.5</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E4752" t="b">
         <v>1</v>
@@ -88449,10 +88449,10 @@
         <v>-2</v>
       </c>
       <c r="C4753" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4753" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E4753" t="b">
         <v>1</v>
@@ -88465,13 +88465,13 @@
         </is>
       </c>
       <c r="B4754" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C4754" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4754" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4754" t="b">
         <v>1</v>
@@ -88487,10 +88487,10 @@
         <v>0</v>
       </c>
       <c r="C4755" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4755" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4755" t="b">
         <v>1</v>
@@ -88504,10 +88504,10 @@
       </c>
       <c r="B4756" t="inlineStr"/>
       <c r="C4756" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4756" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4756" t="b">
         <v>0</v>
@@ -88521,10 +88521,10 @@
       </c>
       <c r="B4757" t="inlineStr"/>
       <c r="C4757" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4757" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4757" t="b">
         <v>0</v>
@@ -88540,10 +88540,10 @@
         <v>-3</v>
       </c>
       <c r="C4758" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4758" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4758" t="b">
         <v>1</v>
@@ -88559,10 +88559,10 @@
         <v>0</v>
       </c>
       <c r="C4759" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4759" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4759" t="b">
         <v>1</v>
@@ -88578,10 +88578,10 @@
         <v>0</v>
       </c>
       <c r="C4760" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D4760" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4760" t="b">
         <v>1</v>
@@ -88600,7 +88600,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4761" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4761" t="b">
         <v>1</v>
@@ -88619,7 +88619,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4762" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E4762" t="b">
         <v>1</v>
@@ -88636,7 +88636,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4763" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E4763" t="b">
         <v>0</v>
@@ -88653,7 +88653,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4764" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E4764" t="b">
         <v>0</v>
@@ -88672,7 +88672,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4765" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4765" t="b">
         <v>1</v>
@@ -88691,7 +88691,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4766" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4766" t="b">
         <v>1</v>
@@ -88710,7 +88710,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4767" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4767" t="b">
         <v>1</v>
@@ -88729,7 +88729,7 @@
         <v>-1</v>
       </c>
       <c r="D4768" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4768" t="b">
         <v>1</v>
@@ -88748,7 +88748,7 @@
         <v>-1</v>
       </c>
       <c r="D4769" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4769" t="b">
         <v>1</v>
@@ -88765,7 +88765,7 @@
         <v>-1</v>
       </c>
       <c r="D4770" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4770" t="b">
         <v>0</v>
@@ -88784,7 +88784,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D4771" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4771" t="b">
         <v>1</v>
@@ -88803,7 +88803,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D4772" t="n">
-        <v>-0.7666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4772" t="b">
         <v>1</v>
@@ -88822,7 +88822,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4773" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4773" t="b">
         <v>1</v>
@@ -88841,7 +88841,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4774" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4774" t="b">
         <v>1</v>
@@ -88860,7 +88860,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4775" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4775" t="b">
         <v>1</v>
@@ -88879,7 +88879,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4776" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4776" t="b">
         <v>1</v>
@@ -88898,7 +88898,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4777" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4777" t="b">
         <v>1</v>
@@ -88915,7 +88915,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4778" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4778" t="b">
         <v>0</v>
@@ -88934,7 +88934,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4779" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4779" t="b">
         <v>1</v>
@@ -88953,7 +88953,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D4780" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4780" t="b">
         <v>1</v>
@@ -88966,13 +88966,13 @@
         </is>
       </c>
       <c r="B4781" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C4781" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4781" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4781" t="b">
         <v>1</v>
@@ -88988,10 +88988,10 @@
         <v>0</v>
       </c>
       <c r="C4782" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4782" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E4782" t="b">
         <v>1</v>
@@ -89007,10 +89007,10 @@
         <v>0</v>
       </c>
       <c r="C4783" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D4783" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4783" t="b">
         <v>1</v>
@@ -89024,10 +89024,10 @@
       </c>
       <c r="B4784" t="inlineStr"/>
       <c r="C4784" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D4784" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4784" t="b">
         <v>0</v>
@@ -89041,10 +89041,10 @@
       </c>
       <c r="B4785" t="inlineStr"/>
       <c r="C4785" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D4785" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4785" t="b">
         <v>0</v>
@@ -89056,15 +89056,17 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B4786" t="inlineStr"/>
+      <c r="B4786" t="n">
+        <v>1</v>
+      </c>
       <c r="C4786" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D4786" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4786" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4787">
@@ -89073,15 +89075,17 @@
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="B4787" t="inlineStr"/>
+      <c r="B4787" t="n">
+        <v>0</v>
+      </c>
       <c r="C4787" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D4787" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E4787" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4788">
@@ -89090,15 +89094,36 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="B4788" t="inlineStr"/>
+      <c r="B4788" t="n">
+        <v>-2</v>
+      </c>
       <c r="C4788" t="n">
-        <v>0</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D4788" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E4788" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4789">
+      <c r="A4789" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B4789" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4789" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="D4789" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E4789" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -89131,7 +89156,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-08 | Publication days: 3666</t>
+          <t>Coverage: 2013-03-01 to 2026-04-09 | Publication days: 3670</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4789"/>
+  <dimension ref="A1:E4790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88408,13 +88408,13 @@
         </is>
       </c>
       <c r="B4751" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C4751" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-1</v>
       </c>
       <c r="D4751" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4751" t="b">
         <v>1</v>
@@ -88430,10 +88430,10 @@
         <v>0</v>
       </c>
       <c r="C4752" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D4752" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E4752" t="b">
         <v>1</v>
@@ -88449,10 +88449,10 @@
         <v>-2</v>
       </c>
       <c r="C4753" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4753" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4753" t="b">
         <v>1</v>
@@ -88465,13 +88465,13 @@
         </is>
       </c>
       <c r="B4754" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C4754" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D4754" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4754" t="b">
         <v>1</v>
@@ -88487,10 +88487,10 @@
         <v>0</v>
       </c>
       <c r="C4755" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D4755" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4755" t="b">
         <v>1</v>
@@ -88504,10 +88504,10 @@
       </c>
       <c r="B4756" t="inlineStr"/>
       <c r="C4756" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D4756" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4756" t="b">
         <v>0</v>
@@ -88521,10 +88521,10 @@
       </c>
       <c r="B4757" t="inlineStr"/>
       <c r="C4757" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D4757" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4757" t="b">
         <v>0</v>
@@ -88540,10 +88540,10 @@
         <v>-3</v>
       </c>
       <c r="C4758" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4758" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4758" t="b">
         <v>1</v>
@@ -88559,10 +88559,10 @@
         <v>0</v>
       </c>
       <c r="C4759" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D4759" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4759" t="b">
         <v>1</v>
@@ -88578,10 +88578,10 @@
         <v>0</v>
       </c>
       <c r="C4760" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D4760" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4760" t="b">
         <v>1</v>
@@ -88600,7 +88600,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4761" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4761" t="b">
         <v>1</v>
@@ -88619,7 +88619,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4762" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4762" t="b">
         <v>1</v>
@@ -88636,7 +88636,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4763" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4763" t="b">
         <v>0</v>
@@ -88653,7 +88653,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4764" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E4764" t="b">
         <v>0</v>
@@ -88672,7 +88672,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4765" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E4765" t="b">
         <v>1</v>
@@ -88691,7 +88691,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4766" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4766" t="b">
         <v>1</v>
@@ -88710,7 +88710,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4767" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4767" t="b">
         <v>1</v>
@@ -88729,7 +88729,7 @@
         <v>-1</v>
       </c>
       <c r="D4768" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4768" t="b">
         <v>1</v>
@@ -88748,7 +88748,7 @@
         <v>-1</v>
       </c>
       <c r="D4769" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4769" t="b">
         <v>1</v>
@@ -88765,7 +88765,7 @@
         <v>-1</v>
       </c>
       <c r="D4770" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4770" t="b">
         <v>0</v>
@@ -88784,7 +88784,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D4771" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4771" t="b">
         <v>1</v>
@@ -88803,7 +88803,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D4772" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E4772" t="b">
         <v>1</v>
@@ -88822,7 +88822,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4773" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E4773" t="b">
         <v>1</v>
@@ -88841,7 +88841,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4774" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E4774" t="b">
         <v>1</v>
@@ -88860,7 +88860,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D4775" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4775" t="b">
         <v>1</v>
@@ -88879,7 +88879,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4776" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="E4776" t="b">
         <v>1</v>
@@ -88898,7 +88898,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D4777" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="E4777" t="b">
         <v>1</v>
@@ -88915,7 +88915,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4778" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="E4778" t="b">
         <v>0</v>
@@ -88934,7 +88934,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4779" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="E4779" t="b">
         <v>1</v>
@@ -88953,7 +88953,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D4780" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="E4780" t="b">
         <v>1</v>
@@ -88972,7 +88972,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D4781" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4781" t="b">
         <v>1</v>
@@ -88991,7 +88991,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D4782" t="n">
-        <v>-0.7</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E4782" t="b">
         <v>1</v>
@@ -89010,7 +89010,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D4783" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E4783" t="b">
         <v>1</v>
@@ -89123,6 +89123,25 @@
         <v>-0.5</v>
       </c>
       <c r="E4789" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4790">
+      <c r="A4790" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B4790" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C4790" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D4790" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E4790" t="b">
         <v>1</v>
       </c>
     </row>
@@ -89156,7 +89175,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-09 | Publication days: 3670</t>
+          <t>Coverage: 2013-03-01 to 2026-04-10 | Publication days: 3671</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4790"/>
+  <dimension ref="A1:E4791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89143,6 +89143,23 @@
       </c>
       <c r="E4790" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4791">
+      <c r="A4791" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B4791" t="inlineStr"/>
+      <c r="C4791" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D4791" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E4791" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -89175,7 +89192,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-10 | Publication days: 3671</t>
+          <t>Coverage: 2013-03-01 to 2026-04-11 | Publication days: 3671</t>
         </is>
       </c>
     </row>

--- a/data/JP.xlsx
+++ b/data/JP.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4791"/>
+  <dimension ref="A1:E4792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89159,6 +89159,23 @@
         <v>-0.7</v>
       </c>
       <c r="E4791" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4792">
+      <c r="A4792" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B4792" t="inlineStr"/>
+      <c r="C4792" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D4792" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E4792" t="b">
         <v>0</v>
       </c>
     </row>
@@ -89192,7 +89209,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2013-03-01 to 2026-04-11 | Publication days: 3671</t>
+          <t>Coverage: 2013-03-01 to 2026-04-12 | Publication days: 3671</t>
         </is>
       </c>
     </row>
